--- a/conformance/fixtures/048-if-and-comparison-boundaries/expected.xlsx
+++ b/conformance/fixtures/048-if-and-comparison-boundaries/expected.xlsx
@@ -480,7 +480,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
